--- a/Modified_And_New_Members.xlsx
+++ b/Modified_And_New_Members.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,6 +555,108 @@
       <c r="AB1" t="inlineStr">
         <is>
           <t>changedByDeviceId</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Lee_New</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Neha</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Ashley</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>LM</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>50007</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>89818</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2022-05-01T00:00:00</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>3924 Oak Ave</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Princeton</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>8540</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>980-365-9837</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>neha.lee7@example.com</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>700-219-2832</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Matthew (10y)</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>modified</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2026-04-20T10:15:42.670000+00:00</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>9f444029-430d-450d-bffb-bce05318973a</t>
         </is>
       </c>
     </row>
